--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486876_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486876_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9785</v>
+        <v>3.3141</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6623</v>
+        <v>4.9616</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3163</v>
+        <v>-1.6475</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.3726</v>
+        <v>0.242</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.5831</v>
+        <v>0.2761</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.7894</v>
+        <v>-0.0341</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.0273</v>
+        <v>3.398</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.0925</v>
+        <v>1.4381</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9349</v>
+        <v>1.9599</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3452</v>
+        <v>-3.1559</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4907</v>
+        <v>-1.1619</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8545</v>
+        <v>-1.994</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0801</v>
+        <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5786</v>
+        <v>-0.893</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2893</v>
+        <v>-1.1858</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2893</v>
+        <v>0.2928</v>
       </c>
       <c r="V2" t="n">
-        <v>3.7191</v>
+        <v>2.117</v>
       </c>
       <c r="W2" t="n">
-        <v>3.427</v>
+        <v>3.7761</v>
       </c>
       <c r="X2" t="n">
-        <v>0.292</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5866</v>
+        <v>2.7903</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5819</v>
+        <v>1.122</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9954</v>
+        <v>1.6684</v>
       </c>
       <c r="G3" t="n">
-        <v>0.242</v>
+        <v>-0.1328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2761</v>
+        <v>-1.1716</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0341</v>
+        <v>1.0388</v>
       </c>
       <c r="J3" t="n">
-        <v>3.398</v>
+        <v>1.8967</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4381</v>
+        <v>-0.2073</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9599</v>
+        <v>2.104</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1559</v>
+        <v>-2.0295</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1619</v>
+        <v>-0.9643</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.994</v>
+        <v>-1.0652</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8748</v>
+        <v>3.2855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6206</v>
+        <v>-0.6974</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5655</v>
+        <v>-0.8178</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9449</v>
+        <v>0.1204</v>
       </c>
       <c r="V3" t="n">
-        <v>2.117</v>
+        <v>1.3618</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7761</v>
+        <v>1.0698</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6591</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0988</v>
+        <v>2.0043</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5754</v>
+        <v>0.8066</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5233</v>
+        <v>1.1977</v>
       </c>
       <c r="G4" t="n">
-        <v>0.969</v>
+        <v>-4.3726</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4479</v>
+        <v>-1.5831</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5211</v>
+        <v>-2.7894</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1369</v>
+        <v>-2.0273</v>
       </c>
       <c r="K4" t="n">
-        <v>1.058</v>
+        <v>-1.0925</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0789</v>
+        <v>-0.9349</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1679</v>
+        <v>-2.3452</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6101</v>
+        <v>-0.4907</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4422</v>
+        <v>-1.8545</v>
       </c>
       <c r="P4" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>3.0801</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2735</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0464</v>
+        <v>0.4336</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2271</v>
+        <v>0.1708</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2402</v>
+        <v>3.7191</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4189</v>
+        <v>3.427</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8705</v>
+        <v>1.9301</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6764</v>
+        <v>2.1663</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1941</v>
+        <v>-0.2362</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1328</v>
+        <v>-0.4296</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1716</v>
+        <v>0.5023</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0388</v>
+        <v>-0.9318</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8967</v>
+        <v>1.6896</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2073</v>
+        <v>0.7431</v>
       </c>
       <c r="L5" t="n">
-        <v>2.104</v>
+        <v>0.9464</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0295</v>
+        <v>-2.1191</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9643</v>
+        <v>-0.2408</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0652</v>
+        <v>-1.8783</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2855</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6173</v>
+        <v>-0.1172</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2634</v>
+        <v>-0.3528</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3539</v>
+        <v>0.2356</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3618</v>
+        <v>0.4234</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0698</v>
+        <v>0.8295</v>
       </c>
       <c r="X5" t="n">
-        <v>0.292</v>
+        <v>-0.4061</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4828</v>
+        <v>1.6277</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5115</v>
+        <v>1.2229</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0287</v>
+        <v>0.4048</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4296</v>
+        <v>0.969</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5023</v>
+        <v>0.4479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9318</v>
+        <v>0.5211</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6896</v>
+        <v>1.1369</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7431</v>
+        <v>1.058</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9464</v>
+        <v>0.0789</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1191</v>
+        <v>-0.1679</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2408</v>
+        <v>-0.6101</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8783</v>
+        <v>0.4422</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5645</v>
+        <v>-0.1976</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0076</v>
+        <v>-0.3062</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4431</v>
+        <v>0.1086</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4234</v>
+        <v>0.2402</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8295</v>
+        <v>1.4189</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4061</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4624</v>
+        <v>-0.4753</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0731</v>
+        <v>-1.4663</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3893</v>
+        <v>0.9911</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3698</v>
+        <v>2.9741</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3698</v>
+        <v>0.5061</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.468</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0195</v>
+        <v>2.5864</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0195</v>
+        <v>0.166</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.4204</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3893</v>
+        <v>0.3876</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3893</v>
+        <v>0.3401</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.0475</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0659</v>
+        <v>0.1889</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0659</v>
+        <v>0.0541</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1348</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5848</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5848</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4739</v>
+        <v>-1.3957</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6867</v>
+        <v>-1.9346</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2128</v>
+        <v>0.5389</v>
       </c>
       <c r="G8" t="n">
         <v>0.1117</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4336</v>
+        <v>-0.3555</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0931</v>
+        <v>-0.341</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3405</v>
+        <v>-0.0144</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7679</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6579</v>
+        <v>-1.4624</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5008</v>
+        <v>-1.0731</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8429</v>
+        <v>-0.3893</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9741</v>
+        <v>-0.3698</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5061</v>
+        <v>-0.3698</v>
       </c>
       <c r="I9" t="n">
-        <v>2.468</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5864</v>
+        <v>0.0195</v>
       </c>
       <c r="K9" t="n">
-        <v>0.166</v>
+        <v>0.0195</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4204</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3876</v>
+        <v>-0.3893</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3401</v>
+        <v>-0.3893</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0475</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9938</v>
+        <v>-0.0659</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9804</v>
+        <v>-0.0659</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0134</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5848</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3084</v>
+        <v>-2.2056</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6653</v>
+        <v>-2.5921</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3569</v>
+        <v>0.3865</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8125</v>
@@ -1234,13 +1234,13 @@
         <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1387</v>
+        <v>-0.0359</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0462</v>
+        <v>0.0269</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0925</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5905</v>
+        <v>-3.6152</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2683</v>
+        <v>0.125</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8588</v>
+        <v>-3.7402</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7317</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7114</v>
+        <v>-0.7362</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4225</v>
+        <v>-0.5658</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2889</v>
+        <v>-0.1704</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1741</v>
@@ -1345,37 +1345,37 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5241</v>
+        <v>2.512299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3499</v>
+        <v>3.338300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8258999999999999</v>
+        <v>-0.8258000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.552200000000001</v>
+        <v>-4.5522</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8277000000000001</v>
+        <v>-0.8276999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.724100000000001</v>
+        <v>-3.7241</v>
       </c>
       <c r="J12" t="n">
-        <v>7.5804</v>
+        <v>7.580400000000002</v>
       </c>
       <c r="K12" t="n">
         <v>4.124099999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>3.456199999999999</v>
+        <v>3.4562</v>
       </c>
       <c r="M12" t="n">
         <v>-12.1325</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.9519</v>
+        <v>-4.951899999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-7.180599999999999</v>
@@ -1390,16 +1390,16 @@
         <v>19.5074</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2937</v>
+        <v>-2.3055</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1089</v>
+        <v>-3.1207</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8151999999999999</v>
+        <v>0.8154</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1561</v>
+        <v>1.156099999999999</v>
       </c>
       <c r="W12" t="n">
         <v>10.1722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8835</v>
+        <v>3.3518</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6475</v>
+        <v>0.1245</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2361</v>
+        <v>3.2273</v>
       </c>
       <c r="G13" t="n">
         <v>2.7308</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1178</v>
+        <v>0.586</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2903</v>
+        <v>-0.2327</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8275</v>
+        <v>0.8187</v>
       </c>
       <c r="V13" t="n">
         <v>0.2402</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4178</v>
+        <v>2.9419</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0815</v>
+        <v>3.14</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6636</v>
+        <v>-0.1981</v>
       </c>
       <c r="G14" t="n">
         <v>3.5501</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0115</v>
+        <v>0.5356</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4411</v>
+        <v>0.4996</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4296</v>
+        <v>0.036</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9384</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5652</v>
+        <v>2.6561</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5853</v>
+        <v>2.201</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0201</v>
+        <v>0.4551</v>
       </c>
       <c r="G15" t="n">
-        <v>0.704</v>
+        <v>1.8195</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5645</v>
+        <v>-1.9432</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1395</v>
+        <v>3.7626</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9538</v>
+        <v>2.9125</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9538</v>
+        <v>-1.31</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.2225</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2498</v>
+        <v>-1.093</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3893</v>
+        <v>-0.6332</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1395</v>
+        <v>-0.4598</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4107</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.6694</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6908</v>
+        <v>-0.0484</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6315</v>
+        <v>-0.3993</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0593</v>
+        <v>0.3509</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2402</v>
+        <v>2.117</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2402</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3625</v>
+        <v>1.3367</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3642</v>
+        <v>0.4396</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0017</v>
+        <v>0.897</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8195</v>
+        <v>0.4475</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9432</v>
+        <v>0.1686</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7626</v>
+        <v>0.2789</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9125</v>
+        <v>0.3893</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.31</v>
+        <v>0.3893</v>
       </c>
       <c r="L16" t="n">
-        <v>4.2225</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.093</v>
+        <v>0.0582</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6332</v>
+        <v>-0.2208</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4598</v>
+        <v>0.2789</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.6694</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.342</v>
+        <v>0.4785</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2361</v>
+        <v>0.0503</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1059</v>
+        <v>0.4282</v>
       </c>
       <c r="V16" t="n">
-        <v>2.117</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9636</v>
+        <v>1.2357</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1258</v>
+        <v>1.1669</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8378</v>
+        <v>0.0688</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4475</v>
+        <v>0.704</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1686</v>
+        <v>0.5645</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2789</v>
+        <v>0.1395</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3893</v>
+        <v>0.9538</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3893</v>
+        <v>0.9538</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0582</v>
+        <v>-0.2498</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2208</v>
+        <v>-0.3893</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2789</v>
+        <v>0.1395</v>
       </c>
       <c r="P17" t="n">
         <v>0.4107</v>
@@ -1780,28 +1780,28 @@
         <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1054</v>
+        <v>0.3613</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2635</v>
+        <v>0.2131</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3689</v>
+        <v>0.1482</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1244</v>
+        <v>0.2334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5897</v>
+        <v>0.9891</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4652</v>
+        <v>-0.7557</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1374</v>
+        <v>1.1624</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2424</v>
+        <v>1.7648</v>
       </c>
       <c r="I18" t="n">
-        <v>1.105</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1172</v>
+        <v>2.7052</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3825</v>
+        <v>2.0347</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4997</v>
+        <v>0.6706</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2545</v>
+        <v>-1.5428</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8599</v>
+        <v>-0.2699</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6054</v>
+        <v>-1.2729</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-2.6694</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>1.118</v>
+        <v>0.9396</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4992</v>
+        <v>-0.3567</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3812</v>
+        <v>1.2963</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2402</v>
+        <v>-1.0472</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3001</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6753</v>
+        <v>-0.4564</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9754</v>
+        <v>-0.1479</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1624</v>
+        <v>-0.1374</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7648</v>
+        <v>-1.2424</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6022999999999999</v>
+        <v>1.105</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7052</v>
+        <v>0.1172</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0347</v>
+        <v>-0.3825</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6706</v>
+        <v>0.4997</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5428</v>
+        <v>-0.2545</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2699</v>
+        <v>-0.8599</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2729</v>
+        <v>0.6054</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.6694</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4061</v>
+        <v>0.3893</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6705</v>
+        <v>0.4532</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0766</v>
+        <v>-0.0638</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0472</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3356</v>
+        <v>-0.9301</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0755</v>
+        <v>-0.1337</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4111</v>
+        <v>-0.7964</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3237</v>
@@ -2014,13 +2014,13 @@
         <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0683</v>
+        <v>0.4737</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0854</v>
+        <v>-0.2946</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1536</v>
+        <v>0.7683</v>
       </c>
       <c r="V20" t="n">
         <v>1.1786</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0711</v>
+        <v>-1.8026</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9231</v>
+        <v>-1.7139</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.148</v>
+        <v>-0.0887</v>
       </c>
       <c r="G21" t="n">
         <v>0.4046</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1054</v>
+        <v>0.3739</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5192</v>
+        <v>-0.31</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6246</v>
+        <v>0.6839</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9384</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8414</v>
+        <v>-3.3707</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8782</v>
+        <v>-1.2506</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9632</v>
+        <v>-2.1201</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2802</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3989</v>
+        <v>0.0718</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9804</v>
+        <v>-0.3527</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5815</v>
+        <v>0.4245</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1088</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.293</v>
+        <v>-5.1772</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5175</v>
+        <v>-3.6807</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7755</v>
+        <v>-1.4966</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5256</v>
@@ -2248,13 +2248,13 @@
         <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5888</v>
+        <v>0.527</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9222</v>
+        <v>-0.0854</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3334</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5242</v>
+        <v>-0.1292999999999997</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8260000000000005</v>
+        <v>0.825800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3499</v>
+        <v>-0.9553000000000003</v>
       </c>
       <c r="G24" t="n">
-        <v>4.551999999999999</v>
+        <v>4.552</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8278000000000008</v>
+        <v>0.8278000000000003</v>
       </c>
       <c r="I24" t="n">
         <v>3.7242</v>
@@ -2326,13 +2326,13 @@
         <v>11.294</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2936</v>
+        <v>4.6883</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8151999999999999</v>
+        <v>-0.8152</v>
       </c>
       <c r="U24" t="n">
-        <v>4.108700000000001</v>
+        <v>5.5036</v>
       </c>
       <c r="V24" t="n">
         <v>-1.156</v>
